--- a/Phylogenetics/pop_gen/results/americanasimple.11.meanQ.humanreadable.xlsx
+++ b/Phylogenetics/pop_gen/results/americanasimple.11.meanQ.humanreadable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanfolk/Documents/GitHub/Heuchera-americana-group-species-manuscript/Phylogenetics/pop_gen/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F451471-0141-7342-9D6F-4CAEFCB490AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CB510456-6242-1C45-8C97-957CEB533F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-180" yWindow="5120" windowWidth="27240" windowHeight="16320" xr2:uid="{88EAF0B3-F387-0949-9C4D-2C22DF997F4A}"/>
   </bookViews>

--- a/Phylogenetics/pop_gen/results/americanasimple.11.meanQ.humanreadable.xlsx
+++ b/Phylogenetics/pop_gen/results/americanasimple.11.meanQ.humanreadable.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanfolk/Documents/GitHub/Heuchera-americana-group-species-manuscript/Phylogenetics/pop_gen/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CB510456-6242-1C45-8C97-957CEB533F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06D1A19-084E-E847-A1BA-FB3597DEB2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="5120" windowWidth="27240" windowHeight="16320" xr2:uid="{88EAF0B3-F387-0949-9C4D-2C22DF997F4A}"/>
+    <workbookView xWindow="0" yWindow="1820" windowWidth="27240" windowHeight="16320" xr2:uid="{88EAF0B3-F387-0949-9C4D-2C22DF997F4A}"/>
   </bookViews>
   <sheets>
     <sheet name="americanasimple.11.meanQ.humanr" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="658">
   <si>
     <t>accession</t>
   </si>
@@ -1991,6 +2004,9 @@
   </si>
   <si>
     <t>fumosimontana</t>
+  </si>
+  <si>
+    <t>Best assignment</t>
   </si>
 </sst>
 </file>
@@ -2851,10 +2867,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D3B96B-9C6C-AA47-B99E-36FC108E554B}">
-  <dimension ref="A1:M632"/>
+  <dimension ref="A1:N632"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2894,8 +2910,11 @@
       <c r="M1" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2935,8 +2954,12 @@
       <c r="M2">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N2" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C2:M2), C2:M2, 0))</f>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2976,8 +2999,12 @@
       <c r="M3">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C3:M3), C3:M3, 0))</f>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3044,12 @@
       <c r="M4">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C4:M4), C4:M4, 0))</f>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3058,8 +3089,12 @@
       <c r="M5">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C5:M5), C5:M5, 0))</f>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -3099,8 +3134,12 @@
       <c r="M6">
         <v>0.96531</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C6:M6), C6:M6, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3140,8 +3179,12 @@
       <c r="M7">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C7:M7), C7:M7, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3181,8 +3224,12 @@
       <c r="M8">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C8:M8), C8:M8, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -3222,8 +3269,12 @@
       <c r="M9">
         <v>0.99986699999999995</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C9:M9), C9:M9, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3263,8 +3314,12 @@
       <c r="M10">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C10:M10), C10:M10, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -3304,8 +3359,12 @@
       <c r="M11">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C11:M11), C11:M11, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3345,8 +3404,12 @@
       <c r="M12">
         <v>0.99987000000000004</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C12:M12), C12:M12, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -3386,8 +3449,12 @@
       <c r="M13">
         <v>0.97927900000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C13:M13), C13:M13, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -3427,8 +3494,12 @@
       <c r="M14">
         <v>0.99987499999999996</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C14:M14), C14:M14, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -3468,8 +3539,12 @@
       <c r="M15">
         <v>0.99986299999999995</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C15:M15), C15:M15, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3509,8 +3584,12 @@
       <c r="M16">
         <v>0.891181</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C16:M16), C16:M16, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -3550,8 +3629,12 @@
       <c r="M17">
         <v>0.99985500000000005</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C17:M17), C17:M17, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -3591,8 +3674,12 @@
       <c r="M18">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C18:M18), C18:M18, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3632,8 +3719,12 @@
       <c r="M19">
         <v>0.96202399999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N19" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C19:M19), C19:M19, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -3673,8 +3764,12 @@
       <c r="M20">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C20:M20), C20:M20, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -3714,8 +3809,12 @@
       <c r="M21">
         <v>0.999861</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C21:M21), C21:M21, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -3755,8 +3854,12 @@
       <c r="M22">
         <v>0.570326</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N22" t="str">
+        <f>INDEX($C$1:$M$1, MATCH(MAX(C22:M22), C22:M22, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -3796,8 +3899,12 @@
       <c r="M23">
         <v>0.53735100000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N23" t="str">
+        <f t="shared" ref="N23:N86" si="0">INDEX($C$1:$M$1, MATCH(MAX(C23:M23), C23:M23, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3837,8 +3944,12 @@
       <c r="M24">
         <v>0.64248899999999998</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N24" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3878,8 +3989,12 @@
       <c r="M25">
         <v>0.66555500000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N25" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -3919,8 +4034,12 @@
       <c r="M26">
         <v>0.47498600000000002</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N26" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -3960,8 +4079,12 @@
       <c r="M27">
         <v>0.46299400000000002</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N27" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -4001,8 +4124,12 @@
       <c r="M28">
         <v>0.45341999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N28" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4042,8 +4169,12 @@
       <c r="M29">
         <v>0.49940000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N29" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4083,8 +4214,12 @@
       <c r="M30">
         <v>0.52985700000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N30" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -4124,8 +4259,12 @@
       <c r="M31">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N31" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -4165,8 +4304,12 @@
       <c r="M32">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N32" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4206,8 +4349,12 @@
       <c r="M33">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N33" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -4247,8 +4394,12 @@
       <c r="M34">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N34" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -4288,8 +4439,12 @@
       <c r="M35">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N35" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -4329,8 +4484,12 @@
       <c r="M36">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N36" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -4370,8 +4529,12 @@
       <c r="M37">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N37" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -4411,8 +4574,12 @@
       <c r="M38">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N38" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -4452,8 +4619,12 @@
       <c r="M39">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N39" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -4493,8 +4664,12 @@
       <c r="M40">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N40" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -4534,8 +4709,12 @@
       <c r="M41">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N41" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -4575,8 +4754,12 @@
       <c r="M42">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N42" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -4616,8 +4799,12 @@
       <c r="M43">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N43" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -4657,8 +4844,12 @@
       <c r="M44">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N44" t="str">
+        <f t="shared" si="0"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4698,8 +4889,12 @@
       <c r="M45">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N45" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -4739,8 +4934,12 @@
       <c r="M46">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N46" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -4780,8 +4979,12 @@
       <c r="M47">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N47" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -4821,8 +5024,12 @@
       <c r="M48">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -4862,8 +5069,12 @@
       <c r="M49">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -4903,8 +5114,12 @@
       <c r="M50">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -4944,8 +5159,12 @@
       <c r="M51">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N51" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -4985,8 +5204,12 @@
       <c r="M52">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N52" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -5026,8 +5249,12 @@
       <c r="M53">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N53" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -5067,8 +5294,12 @@
       <c r="M54">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N54" t="str">
+        <f t="shared" si="0"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -5108,8 +5339,12 @@
       <c r="M55">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N55" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -5149,8 +5384,12 @@
       <c r="M56">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N56" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -5190,8 +5429,12 @@
       <c r="M57">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -5231,8 +5474,12 @@
       <c r="M58">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N58" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -5272,8 +5519,12 @@
       <c r="M59">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N59" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5564,12 @@
       <c r="M60">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N60" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -5354,8 +5609,12 @@
       <c r="M61">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N61" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -5395,8 +5654,12 @@
       <c r="M62">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N62" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -5436,8 +5699,12 @@
       <c r="M63">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N63" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -5477,8 +5744,12 @@
       <c r="M64">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N64" t="str">
+        <f t="shared" si="0"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -5518,8 +5789,12 @@
       <c r="M65">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N65" t="str">
+        <f t="shared" si="0"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -5559,8 +5834,12 @@
       <c r="M66">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N66" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -5600,8 +5879,12 @@
       <c r="M67">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N67" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -5641,8 +5924,12 @@
       <c r="M68">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N68" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -5682,8 +5969,12 @@
       <c r="M69">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N69" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -5723,8 +6014,12 @@
       <c r="M70">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N70" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -5764,8 +6059,12 @@
       <c r="M71">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N71" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -5805,8 +6104,12 @@
       <c r="M72">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N72" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -5846,8 +6149,12 @@
       <c r="M73">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N73" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -5887,8 +6194,12 @@
       <c r="M74">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N74" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -5928,8 +6239,12 @@
       <c r="M75">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N75" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -5969,8 +6284,12 @@
       <c r="M76">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N76" t="str">
+        <f t="shared" si="0"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -6010,8 +6329,12 @@
       <c r="M77">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N77" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -6051,8 +6374,12 @@
       <c r="M78">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N78" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -6092,8 +6419,12 @@
       <c r="M79">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N79" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -6133,8 +6464,12 @@
       <c r="M80">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N80" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -6174,8 +6509,12 @@
       <c r="M81">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N81" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -6215,8 +6554,12 @@
       <c r="M82">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N82" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -6256,8 +6599,12 @@
       <c r="M83">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N83" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>89</v>
       </c>
@@ -6297,8 +6644,12 @@
       <c r="M84">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N84" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>90</v>
       </c>
@@ -6338,8 +6689,12 @@
       <c r="M85">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N85" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -6379,8 +6734,12 @@
       <c r="M86">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N86" t="str">
+        <f t="shared" si="0"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -6420,8 +6779,12 @@
       <c r="M87">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N87" t="str">
+        <f t="shared" ref="N87:N150" si="1">INDEX($C$1:$M$1, MATCH(MAX(C87:M87), C87:M87, 0))</f>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -6461,8 +6824,12 @@
       <c r="M88">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N88" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -6502,8 +6869,12 @@
       <c r="M89">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N89" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>95</v>
       </c>
@@ -6543,8 +6914,12 @@
       <c r="M90">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N90" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>96</v>
       </c>
@@ -6584,8 +6959,12 @@
       <c r="M91">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N91" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -6625,8 +7004,12 @@
       <c r="M92">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N92" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>98</v>
       </c>
@@ -6666,8 +7049,12 @@
       <c r="M93">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N93" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>99</v>
       </c>
@@ -6707,8 +7094,12 @@
       <c r="M94">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N94" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>100</v>
       </c>
@@ -6748,8 +7139,12 @@
       <c r="M95">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N95" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>101</v>
       </c>
@@ -6789,8 +7184,12 @@
       <c r="M96">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N96" t="str">
+        <f t="shared" si="1"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>102</v>
       </c>
@@ -6830,8 +7229,12 @@
       <c r="M97">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N97" t="str">
+        <f t="shared" si="1"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>103</v>
       </c>
@@ -6871,8 +7274,12 @@
       <c r="M98">
         <v>1.7056000000000002E-2</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N98" t="str">
+        <f t="shared" si="1"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -6912,8 +7319,12 @@
       <c r="M99">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N99" t="str">
+        <f t="shared" si="1"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>105</v>
       </c>
@@ -6953,8 +7364,12 @@
       <c r="M100">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N100" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>106</v>
       </c>
@@ -6994,8 +7409,12 @@
       <c r="M101">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N101" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -7035,8 +7454,12 @@
       <c r="M102">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N102" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>108</v>
       </c>
@@ -7076,8 +7499,12 @@
       <c r="M103">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N103" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>109</v>
       </c>
@@ -7117,8 +7544,12 @@
       <c r="M104">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N104" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>110</v>
       </c>
@@ -7158,8 +7589,12 @@
       <c r="M105">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N105" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>111</v>
       </c>
@@ -7199,8 +7634,12 @@
       <c r="M106">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N106" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>112</v>
       </c>
@@ -7240,8 +7679,12 @@
       <c r="M107">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N107" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>113</v>
       </c>
@@ -7281,8 +7724,12 @@
       <c r="M108">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N108" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -7322,8 +7769,12 @@
       <c r="M109">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N109" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>115</v>
       </c>
@@ -7363,8 +7814,12 @@
       <c r="M110">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N110" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>116</v>
       </c>
@@ -7404,8 +7859,12 @@
       <c r="M111">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N111" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>117</v>
       </c>
@@ -7445,8 +7904,12 @@
       <c r="M112">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N112" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>118</v>
       </c>
@@ -7486,8 +7949,12 @@
       <c r="M113">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N113" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>119</v>
       </c>
@@ -7527,8 +7994,12 @@
       <c r="M114">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N114" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -7568,8 +8039,12 @@
       <c r="M115">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N115" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>121</v>
       </c>
@@ -7609,8 +8084,12 @@
       <c r="M116">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N116" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>122</v>
       </c>
@@ -7650,8 +8129,12 @@
       <c r="M117">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N117" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>123</v>
       </c>
@@ -7691,8 +8174,12 @@
       <c r="M118">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N118" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -7732,8 +8219,12 @@
       <c r="M119">
         <v>5.7876999999999998E-2</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N119" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -7773,8 +8264,12 @@
       <c r="M120">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N120" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -7814,8 +8309,12 @@
       <c r="M121">
         <v>5.7172000000000001E-2</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N121" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -7855,8 +8354,12 @@
       <c r="M122">
         <v>2.8868000000000001E-2</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N122" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>128</v>
       </c>
@@ -7896,8 +8399,12 @@
       <c r="M123">
         <v>8.2472000000000004E-2</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N123" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>129</v>
       </c>
@@ -7937,8 +8444,12 @@
       <c r="M124">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N124" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>130</v>
       </c>
@@ -7978,8 +8489,12 @@
       <c r="M125">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N125" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>131</v>
       </c>
@@ -8019,8 +8534,12 @@
       <c r="M126">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N126" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -8060,8 +8579,12 @@
       <c r="M127">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N127" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>133</v>
       </c>
@@ -8101,8 +8624,12 @@
       <c r="M128">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N128" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>134</v>
       </c>
@@ -8142,8 +8669,12 @@
       <c r="M129">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N129" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>135</v>
       </c>
@@ -8183,8 +8714,12 @@
       <c r="M130">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N130" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>136</v>
       </c>
@@ -8224,8 +8759,12 @@
       <c r="M131">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N131" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -8265,8 +8804,12 @@
       <c r="M132">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N132" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>138</v>
       </c>
@@ -8306,8 +8849,12 @@
       <c r="M133">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N133" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -8347,8 +8894,12 @@
       <c r="M134">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N134" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -8388,8 +8939,12 @@
       <c r="M135">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N135" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -8429,8 +8984,12 @@
       <c r="M136">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N136" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -8470,8 +9029,12 @@
       <c r="M137">
         <v>0.36457699999999998</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N137" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -8511,8 +9074,12 @@
       <c r="M138">
         <v>6.0906000000000002E-2</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N138" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>144</v>
       </c>
@@ -8552,8 +9119,12 @@
       <c r="M139">
         <v>7.3090000000000002E-2</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N139" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -8593,8 +9164,12 @@
       <c r="M140">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N140" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>146</v>
       </c>
@@ -8634,8 +9209,12 @@
       <c r="M141">
         <v>7.2819999999999996E-2</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N141" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>147</v>
       </c>
@@ -8675,8 +9254,12 @@
       <c r="M142">
         <v>9.2058000000000001E-2</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N142" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>148</v>
       </c>
@@ -8716,8 +9299,12 @@
       <c r="M143">
         <v>9.7903000000000004E-2</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N143" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>149</v>
       </c>
@@ -8757,8 +9344,12 @@
       <c r="M144">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N144" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>150</v>
       </c>
@@ -8798,8 +9389,12 @@
       <c r="M145">
         <v>5.3768999999999997E-2</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N145" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>151</v>
       </c>
@@ -8839,8 +9434,12 @@
       <c r="M146">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N146" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>152</v>
       </c>
@@ -8880,8 +9479,12 @@
       <c r="M147">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N147" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>153</v>
       </c>
@@ -8921,8 +9524,12 @@
       <c r="M148">
         <v>5.8458000000000003E-2</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N148" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>154</v>
       </c>
@@ -8962,8 +9569,12 @@
       <c r="M149">
         <v>5.6426999999999998E-2</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N149" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>155</v>
       </c>
@@ -9003,8 +9614,12 @@
       <c r="M150">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N150" t="str">
+        <f t="shared" si="1"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>156</v>
       </c>
@@ -9044,8 +9659,12 @@
       <c r="M151">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N151" t="str">
+        <f t="shared" ref="N151:N214" si="2">INDEX($C$1:$M$1, MATCH(MAX(C151:M151), C151:M151, 0))</f>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>157</v>
       </c>
@@ -9085,8 +9704,12 @@
       <c r="M152">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N152" t="str">
+        <f t="shared" si="2"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>158</v>
       </c>
@@ -9126,8 +9749,12 @@
       <c r="M153">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N153" t="str">
+        <f t="shared" si="2"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>159</v>
       </c>
@@ -9167,8 +9794,12 @@
       <c r="M154">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N154" t="str">
+        <f t="shared" si="2"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>160</v>
       </c>
@@ -9208,8 +9839,12 @@
       <c r="M155">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N155" t="str">
+        <f t="shared" si="2"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>161</v>
       </c>
@@ -9249,8 +9884,12 @@
       <c r="M156">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N156" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -9290,8 +9929,12 @@
       <c r="M157">
         <v>0.133516</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N157" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>163</v>
       </c>
@@ -9331,8 +9974,12 @@
       <c r="M158">
         <v>0.13809099999999999</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N158" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>164</v>
       </c>
@@ -9372,8 +10019,12 @@
       <c r="M159">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N159" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>165</v>
       </c>
@@ -9413,8 +10064,12 @@
       <c r="M160">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N160" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -9454,8 +10109,12 @@
       <c r="M161">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N161" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>167</v>
       </c>
@@ -9495,8 +10154,12 @@
       <c r="M162">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N162" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>168</v>
       </c>
@@ -9536,8 +10199,12 @@
       <c r="M163">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N163" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>169</v>
       </c>
@@ -9577,8 +10244,12 @@
       <c r="M164">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N164" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>170</v>
       </c>
@@ -9618,8 +10289,12 @@
       <c r="M165">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N165" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>171</v>
       </c>
@@ -9659,8 +10334,12 @@
       <c r="M166">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N166" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>172</v>
       </c>
@@ -9700,8 +10379,12 @@
       <c r="M167">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N167" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>173</v>
       </c>
@@ -9741,8 +10424,12 @@
       <c r="M168">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N168" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>174</v>
       </c>
@@ -9782,8 +10469,12 @@
       <c r="M169">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N169" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>175</v>
       </c>
@@ -9823,8 +10514,12 @@
       <c r="M170">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N170" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>176</v>
       </c>
@@ -9864,8 +10559,12 @@
       <c r="M171">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N171" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>177</v>
       </c>
@@ -9905,8 +10604,12 @@
       <c r="M172">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N172" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>178</v>
       </c>
@@ -9946,8 +10649,12 @@
       <c r="M173">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N173" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>179</v>
       </c>
@@ -9987,8 +10694,12 @@
       <c r="M174">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N174" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>180</v>
       </c>
@@ -10028,8 +10739,12 @@
       <c r="M175">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N175" t="str">
+        <f t="shared" si="2"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>181</v>
       </c>
@@ -10069,8 +10784,12 @@
       <c r="M176">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N176" t="str">
+        <f t="shared" si="2"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>182</v>
       </c>
@@ -10110,8 +10829,12 @@
       <c r="M177">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N177" t="str">
+        <f t="shared" si="2"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>183</v>
       </c>
@@ -10151,8 +10874,12 @@
       <c r="M178">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N178" t="str">
+        <f t="shared" si="2"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>184</v>
       </c>
@@ -10192,8 +10919,12 @@
       <c r="M179">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N179" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>185</v>
       </c>
@@ -10233,8 +10964,12 @@
       <c r="M180">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N180" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>186</v>
       </c>
@@ -10274,8 +11009,12 @@
       <c r="M181">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N181" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>187</v>
       </c>
@@ -10315,8 +11054,12 @@
       <c r="M182">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N182" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>188</v>
       </c>
@@ -10356,8 +11099,12 @@
       <c r="M183">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N183" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>189</v>
       </c>
@@ -10397,8 +11144,12 @@
       <c r="M184">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N184" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -10438,8 +11189,12 @@
       <c r="M185">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N185" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>191</v>
       </c>
@@ -10479,8 +11234,12 @@
       <c r="M186">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N186" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>192</v>
       </c>
@@ -10520,8 +11279,12 @@
       <c r="M187">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N187" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>193</v>
       </c>
@@ -10561,8 +11324,12 @@
       <c r="M188">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N188" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>194</v>
       </c>
@@ -10602,8 +11369,12 @@
       <c r="M189">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N189" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>195</v>
       </c>
@@ -10643,8 +11414,12 @@
       <c r="M190">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N190" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>196</v>
       </c>
@@ -10684,8 +11459,12 @@
       <c r="M191">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N191" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>197</v>
       </c>
@@ -10725,8 +11504,12 @@
       <c r="M192">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N192" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>198</v>
       </c>
@@ -10766,8 +11549,12 @@
       <c r="M193">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N193" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -10807,8 +11594,12 @@
       <c r="M194">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N194" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>200</v>
       </c>
@@ -10848,8 +11639,12 @@
       <c r="M195">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N195" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>201</v>
       </c>
@@ -10889,8 +11684,12 @@
       <c r="M196">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N196" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>202</v>
       </c>
@@ -10930,8 +11729,12 @@
       <c r="M197">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N197" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>203</v>
       </c>
@@ -10971,8 +11774,12 @@
       <c r="M198">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N198" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>204</v>
       </c>
@@ -11012,8 +11819,12 @@
       <c r="M199">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N199" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>205</v>
       </c>
@@ -11053,8 +11864,12 @@
       <c r="M200">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N200" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>206</v>
       </c>
@@ -11094,8 +11909,12 @@
       <c r="M201">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N201" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>207</v>
       </c>
@@ -11135,8 +11954,12 @@
       <c r="M202">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N202" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>208</v>
       </c>
@@ -11176,8 +11999,12 @@
       <c r="M203">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N203" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>209</v>
       </c>
@@ -11217,8 +12044,12 @@
       <c r="M204">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N204" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>210</v>
       </c>
@@ -11258,8 +12089,12 @@
       <c r="M205">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N205" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>211</v>
       </c>
@@ -11299,8 +12134,12 @@
       <c r="M206">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N206" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>212</v>
       </c>
@@ -11340,8 +12179,12 @@
       <c r="M207">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N207" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>213</v>
       </c>
@@ -11381,8 +12224,12 @@
       <c r="M208">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N208" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>214</v>
       </c>
@@ -11422,8 +12269,12 @@
       <c r="M209">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N209" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>215</v>
       </c>
@@ -11463,8 +12314,12 @@
       <c r="M210">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N210" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>216</v>
       </c>
@@ -11504,8 +12359,12 @@
       <c r="M211">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N211" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>217</v>
       </c>
@@ -11545,8 +12404,12 @@
       <c r="M212">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N212" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>218</v>
       </c>
@@ -11586,8 +12449,12 @@
       <c r="M213">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N213" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>219</v>
       </c>
@@ -11627,8 +12494,12 @@
       <c r="M214">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N214" t="str">
+        <f t="shared" si="2"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>220</v>
       </c>
@@ -11668,8 +12539,12 @@
       <c r="M215">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N215" t="str">
+        <f t="shared" ref="N215:N278" si="3">INDEX($C$1:$M$1, MATCH(MAX(C215:M215), C215:M215, 0))</f>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>222</v>
       </c>
@@ -11709,8 +12584,12 @@
       <c r="M216">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N216" t="str">
+        <f t="shared" si="3"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>223</v>
       </c>
@@ -11750,8 +12629,12 @@
       <c r="M217">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N217" t="str">
+        <f t="shared" si="3"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>224</v>
       </c>
@@ -11791,8 +12674,12 @@
       <c r="M218">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N218" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>225</v>
       </c>
@@ -11832,8 +12719,12 @@
       <c r="M219">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N219" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>226</v>
       </c>
@@ -11873,8 +12764,12 @@
       <c r="M220">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N220" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>227</v>
       </c>
@@ -11914,8 +12809,12 @@
       <c r="M221">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N221" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>228</v>
       </c>
@@ -11955,8 +12854,12 @@
       <c r="M222">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N222" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>229</v>
       </c>
@@ -11996,8 +12899,12 @@
       <c r="M223">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N223" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>230</v>
       </c>
@@ -12037,8 +12944,12 @@
       <c r="M224">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N224" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>231</v>
       </c>
@@ -12078,8 +12989,12 @@
       <c r="M225">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N225" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>232</v>
       </c>
@@ -12119,8 +13034,12 @@
       <c r="M226">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N226" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>233</v>
       </c>
@@ -12160,8 +13079,12 @@
       <c r="M227">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N227" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>234</v>
       </c>
@@ -12201,8 +13124,12 @@
       <c r="M228">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N228" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>235</v>
       </c>
@@ -12242,8 +13169,12 @@
       <c r="M229">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N229" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>236</v>
       </c>
@@ -12283,8 +13214,12 @@
       <c r="M230">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N230" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>237</v>
       </c>
@@ -12324,8 +13259,12 @@
       <c r="M231">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N231" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>239</v>
       </c>
@@ -12365,8 +13304,12 @@
       <c r="M232">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N232" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>240</v>
       </c>
@@ -12406,8 +13349,12 @@
       <c r="M233">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N233" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>241</v>
       </c>
@@ -12447,8 +13394,12 @@
       <c r="M234">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N234" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>242</v>
       </c>
@@ -12488,8 +13439,12 @@
       <c r="M235">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N235" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>243</v>
       </c>
@@ -12529,8 +13484,12 @@
       <c r="M236">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N236" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>244</v>
       </c>
@@ -12570,8 +13529,12 @@
       <c r="M237">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N237" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>246</v>
       </c>
@@ -12611,8 +13574,12 @@
       <c r="M238">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N238" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>247</v>
       </c>
@@ -12652,8 +13619,12 @@
       <c r="M239">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N239" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>248</v>
       </c>
@@ -12693,8 +13664,12 @@
       <c r="M240">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N240" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>249</v>
       </c>
@@ -12734,8 +13709,12 @@
       <c r="M241">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N241" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>250</v>
       </c>
@@ -12775,8 +13754,12 @@
       <c r="M242">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N242" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>251</v>
       </c>
@@ -12816,8 +13799,12 @@
       <c r="M243">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N243" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>252</v>
       </c>
@@ -12857,8 +13844,12 @@
       <c r="M244">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N244" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>253</v>
       </c>
@@ -12898,8 +13889,12 @@
       <c r="M245">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N245" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>254</v>
       </c>
@@ -12939,8 +13934,12 @@
       <c r="M246">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N246" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>255</v>
       </c>
@@ -12980,8 +13979,12 @@
       <c r="M247">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N247" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>256</v>
       </c>
@@ -13021,8 +14024,12 @@
       <c r="M248">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N248" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>257</v>
       </c>
@@ -13062,8 +14069,12 @@
       <c r="M249">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N249" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>258</v>
       </c>
@@ -13103,8 +14114,12 @@
       <c r="M250">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N250" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>259</v>
       </c>
@@ -13144,8 +14159,12 @@
       <c r="M251">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N251" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>260</v>
       </c>
@@ -13185,8 +14204,12 @@
       <c r="M252">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N252" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>261</v>
       </c>
@@ -13226,8 +14249,12 @@
       <c r="M253">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N253" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>262</v>
       </c>
@@ -13267,8 +14294,12 @@
       <c r="M254">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N254" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>263</v>
       </c>
@@ -13308,8 +14339,12 @@
       <c r="M255">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N255" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>264</v>
       </c>
@@ -13349,8 +14384,12 @@
       <c r="M256">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N256" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>265</v>
       </c>
@@ -13390,8 +14429,12 @@
       <c r="M257">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N257" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>266</v>
       </c>
@@ -13431,8 +14474,12 @@
       <c r="M258">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N258" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>267</v>
       </c>
@@ -13472,8 +14519,12 @@
       <c r="M259">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N259" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>268</v>
       </c>
@@ -13513,8 +14564,12 @@
       <c r="M260">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N260" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>269</v>
       </c>
@@ -13554,8 +14609,12 @@
       <c r="M261">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N261" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>270</v>
       </c>
@@ -13595,8 +14654,12 @@
       <c r="M262">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N262" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>271</v>
       </c>
@@ -13636,8 +14699,12 @@
       <c r="M263">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N263" t="str">
+        <f t="shared" si="3"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>272</v>
       </c>
@@ -13677,8 +14744,12 @@
       <c r="M264">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N264" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>273</v>
       </c>
@@ -13718,8 +14789,12 @@
       <c r="M265">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N265" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>274</v>
       </c>
@@ -13759,8 +14834,12 @@
       <c r="M266">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N266" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>275</v>
       </c>
@@ -13800,8 +14879,12 @@
       <c r="M267">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N267" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>276</v>
       </c>
@@ -13841,8 +14924,12 @@
       <c r="M268">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N268" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>277</v>
       </c>
@@ -13882,8 +14969,12 @@
       <c r="M269">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N269" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>278</v>
       </c>
@@ -13923,8 +15014,12 @@
       <c r="M270">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N270" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>279</v>
       </c>
@@ -13964,8 +15059,12 @@
       <c r="M271">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N271" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>280</v>
       </c>
@@ -14005,8 +15104,12 @@
       <c r="M272">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N272" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>281</v>
       </c>
@@ -14046,8 +15149,12 @@
       <c r="M273">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N273" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>282</v>
       </c>
@@ -14087,8 +15194,12 @@
       <c r="M274">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N274" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>283</v>
       </c>
@@ -14128,8 +15239,12 @@
       <c r="M275">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N275" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>284</v>
       </c>
@@ -14169,8 +15284,12 @@
       <c r="M276">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N276" t="str">
+        <f t="shared" si="3"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>285</v>
       </c>
@@ -14210,8 +15329,12 @@
       <c r="M277">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N277" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>286</v>
       </c>
@@ -14251,8 +15374,12 @@
       <c r="M278">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N278" t="str">
+        <f t="shared" si="3"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>287</v>
       </c>
@@ -14292,8 +15419,12 @@
       <c r="M279">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N279" t="str">
+        <f t="shared" ref="N279:N342" si="4">INDEX($C$1:$M$1, MATCH(MAX(C279:M279), C279:M279, 0))</f>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>288</v>
       </c>
@@ -14333,8 +15464,12 @@
       <c r="M280">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N280" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>289</v>
       </c>
@@ -14374,8 +15509,12 @@
       <c r="M281">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N281" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>290</v>
       </c>
@@ -14415,8 +15554,12 @@
       <c r="M282">
         <v>0.363757</v>
       </c>
-    </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N282" t="str">
+        <f t="shared" si="4"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>291</v>
       </c>
@@ -14456,8 +15599,12 @@
       <c r="M283">
         <v>0.377189</v>
       </c>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N283" t="str">
+        <f t="shared" si="4"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>292</v>
       </c>
@@ -14497,8 +15644,12 @@
       <c r="M284">
         <v>0.30758799999999997</v>
       </c>
-    </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N284" t="str">
+        <f t="shared" si="4"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>293</v>
       </c>
@@ -14538,8 +15689,12 @@
       <c r="M285">
         <v>7.1122000000000005E-2</v>
       </c>
-    </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N285" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>294</v>
       </c>
@@ -14579,8 +15734,12 @@
       <c r="M286">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N286" t="str">
+        <f t="shared" si="4"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>295</v>
       </c>
@@ -14620,8 +15779,12 @@
       <c r="M287">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N287" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>296</v>
       </c>
@@ -14661,8 +15824,12 @@
       <c r="M288">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N288" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>297</v>
       </c>
@@ -14702,8 +15869,12 @@
       <c r="M289">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N289" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>298</v>
       </c>
@@ -14743,8 +15914,12 @@
       <c r="M290">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N290" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>299</v>
       </c>
@@ -14784,8 +15959,12 @@
       <c r="M291">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N291" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>300</v>
       </c>
@@ -14825,8 +16004,12 @@
       <c r="M292">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N292" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>301</v>
       </c>
@@ -14866,8 +16049,12 @@
       <c r="M293">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N293" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>302</v>
       </c>
@@ -14907,8 +16094,12 @@
       <c r="M294">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N294" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>303</v>
       </c>
@@ -14948,8 +16139,12 @@
       <c r="M295">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N295" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>304</v>
       </c>
@@ -14989,8 +16184,12 @@
       <c r="M296">
         <v>0.12296600000000001</v>
       </c>
-    </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N296" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>305</v>
       </c>
@@ -15030,8 +16229,12 @@
       <c r="M297">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N297" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>306</v>
       </c>
@@ -15071,8 +16274,12 @@
       <c r="M298">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N298" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>307</v>
       </c>
@@ -15112,8 +16319,12 @@
       <c r="M299">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N299" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>308</v>
       </c>
@@ -15153,8 +16364,12 @@
       <c r="M300">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N300" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>309</v>
       </c>
@@ -15194,8 +16409,12 @@
       <c r="M301">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N301" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>310</v>
       </c>
@@ -15235,8 +16454,12 @@
       <c r="M302">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N302" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>311</v>
       </c>
@@ -15276,8 +16499,12 @@
       <c r="M303">
         <v>7.9879000000000006E-2</v>
       </c>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N303" t="str">
+        <f t="shared" si="4"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>312</v>
       </c>
@@ -15317,8 +16544,12 @@
       <c r="M304">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N304" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>313</v>
       </c>
@@ -15358,8 +16589,12 @@
       <c r="M305">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N305" t="str">
+        <f t="shared" si="4"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>314</v>
       </c>
@@ -15399,8 +16634,12 @@
       <c r="M306">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N306" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>315</v>
       </c>
@@ -15440,8 +16679,12 @@
       <c r="M307">
         <v>9.2289999999999997E-2</v>
       </c>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N307" t="str">
+        <f t="shared" si="4"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>316</v>
       </c>
@@ -15481,8 +16724,12 @@
       <c r="M308">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N308" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>317</v>
       </c>
@@ -15522,8 +16769,12 @@
       <c r="M309">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N309" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>318</v>
       </c>
@@ -15563,8 +16814,12 @@
       <c r="M310">
         <v>6.0072E-2</v>
       </c>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N310" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>319</v>
       </c>
@@ -15604,8 +16859,12 @@
       <c r="M311">
         <v>7.5031E-2</v>
       </c>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N311" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>320</v>
       </c>
@@ -15645,8 +16904,12 @@
       <c r="M312">
         <v>5.1672999999999997E-2</v>
       </c>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N312" t="str">
+        <f t="shared" si="4"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>321</v>
       </c>
@@ -15686,8 +16949,12 @@
       <c r="M313">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N313" t="str">
+        <f t="shared" si="4"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>322</v>
       </c>
@@ -15727,8 +16994,12 @@
       <c r="M314">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N314" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>323</v>
       </c>
@@ -15768,8 +17039,12 @@
       <c r="M315">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N315" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>324</v>
       </c>
@@ -15809,8 +17084,12 @@
       <c r="M316">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N316" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>325</v>
       </c>
@@ -15850,8 +17129,12 @@
       <c r="M317">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N317" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>326</v>
       </c>
@@ -15891,8 +17174,12 @@
       <c r="M318">
         <v>3.4262000000000001E-2</v>
       </c>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N318" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>327</v>
       </c>
@@ -15932,8 +17219,12 @@
       <c r="M319">
         <v>0.19952500000000001</v>
       </c>
-    </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N319" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>328</v>
       </c>
@@ -15973,8 +17264,12 @@
       <c r="M320">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N320" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>329</v>
       </c>
@@ -16014,8 +17309,12 @@
       <c r="M321">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N321" t="str">
+        <f t="shared" si="4"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>331</v>
       </c>
@@ -16055,8 +17354,12 @@
       <c r="M322">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N322" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>332</v>
       </c>
@@ -16096,8 +17399,12 @@
       <c r="M323">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N323" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>333</v>
       </c>
@@ -16137,8 +17444,12 @@
       <c r="M324">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N324" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>334</v>
       </c>
@@ -16178,8 +17489,12 @@
       <c r="M325">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N325" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>335</v>
       </c>
@@ -16219,8 +17534,12 @@
       <c r="M326">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N326" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>336</v>
       </c>
@@ -16260,8 +17579,12 @@
       <c r="M327">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N327" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>337</v>
       </c>
@@ -16301,8 +17624,12 @@
       <c r="M328">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N328" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>338</v>
       </c>
@@ -16342,8 +17669,12 @@
       <c r="M329">
         <v>0.248196</v>
       </c>
-    </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N329" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>339</v>
       </c>
@@ -16383,8 +17714,12 @@
       <c r="M330">
         <v>0.15703600000000001</v>
       </c>
-    </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N330" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>340</v>
       </c>
@@ -16424,8 +17759,12 @@
       <c r="M331">
         <v>0.118962</v>
       </c>
-    </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N331" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>341</v>
       </c>
@@ -16465,8 +17804,12 @@
       <c r="M332">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N332" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>342</v>
       </c>
@@ -16506,8 +17849,12 @@
       <c r="M333">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N333" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>343</v>
       </c>
@@ -16547,8 +17894,12 @@
       <c r="M334">
         <v>0.34441699999999997</v>
       </c>
-    </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N334" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>344</v>
       </c>
@@ -16588,8 +17939,12 @@
       <c r="M335">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N335" t="str">
+        <f t="shared" si="4"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>345</v>
       </c>
@@ -16629,8 +17984,12 @@
       <c r="M336">
         <v>0.43251600000000001</v>
       </c>
-    </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N336" t="str">
+        <f t="shared" si="4"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>346</v>
       </c>
@@ -16670,8 +18029,12 @@
       <c r="M337">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N337" t="str">
+        <f t="shared" si="4"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>347</v>
       </c>
@@ -16711,8 +18074,12 @@
       <c r="M338">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N338" t="str">
+        <f t="shared" si="4"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>348</v>
       </c>
@@ -16752,8 +18119,12 @@
       <c r="M339">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N339" t="str">
+        <f t="shared" si="4"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>349</v>
       </c>
@@ -16793,8 +18164,12 @@
       <c r="M340">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N340" t="str">
+        <f t="shared" si="4"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>350</v>
       </c>
@@ -16834,8 +18209,12 @@
       <c r="M341">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N341" t="str">
+        <f t="shared" si="4"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>351</v>
       </c>
@@ -16875,8 +18254,12 @@
       <c r="M342">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N342" t="str">
+        <f t="shared" si="4"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>352</v>
       </c>
@@ -16916,8 +18299,12 @@
       <c r="M343">
         <v>0.68700399999999995</v>
       </c>
-    </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N343" t="str">
+        <f t="shared" ref="N343:N406" si="5">INDEX($C$1:$M$1, MATCH(MAX(C343:M343), C343:M343, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>353</v>
       </c>
@@ -16957,8 +18344,12 @@
       <c r="M344">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N344" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>354</v>
       </c>
@@ -16998,8 +18389,12 @@
       <c r="M345">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N345" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>355</v>
       </c>
@@ -17039,8 +18434,12 @@
       <c r="M346">
         <v>4.9057999999999997E-2</v>
       </c>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N346" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>356</v>
       </c>
@@ -17080,8 +18479,12 @@
       <c r="M347">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N347" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>357</v>
       </c>
@@ -17121,8 +18524,12 @@
       <c r="M348">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N348" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>358</v>
       </c>
@@ -17162,8 +18569,12 @@
       <c r="M349">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N349" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>359</v>
       </c>
@@ -17203,8 +18614,12 @@
       <c r="M350">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N350" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>360</v>
       </c>
@@ -17244,8 +18659,12 @@
       <c r="M351">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N351" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>361</v>
       </c>
@@ -17285,8 +18704,12 @@
       <c r="M352">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N352" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>362</v>
       </c>
@@ -17326,8 +18749,12 @@
       <c r="M353">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N353" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>363</v>
       </c>
@@ -17367,8 +18794,12 @@
       <c r="M354">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N354" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>364</v>
       </c>
@@ -17408,8 +18839,12 @@
       <c r="M355">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N355" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>365</v>
       </c>
@@ -17449,8 +18884,12 @@
       <c r="M356">
         <v>0.43922800000000001</v>
       </c>
-    </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N356" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>366</v>
       </c>
@@ -17490,8 +18929,12 @@
       <c r="M357">
         <v>0.25876199999999999</v>
       </c>
-    </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N357" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>367</v>
       </c>
@@ -17531,8 +18974,12 @@
       <c r="M358">
         <v>0.258967</v>
       </c>
-    </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N358" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>368</v>
       </c>
@@ -17572,8 +19019,12 @@
       <c r="M359">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N359" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>369</v>
       </c>
@@ -17613,8 +19064,12 @@
       <c r="M360">
         <v>3.9047999999999999E-2</v>
       </c>
-    </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N360" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>370</v>
       </c>
@@ -17654,8 +19109,12 @@
       <c r="M361">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N361" t="str">
+        <f t="shared" si="5"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>371</v>
       </c>
@@ -17695,8 +19154,12 @@
       <c r="M362">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N362" t="str">
+        <f t="shared" si="5"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>372</v>
       </c>
@@ -17736,8 +19199,12 @@
       <c r="M363">
         <v>0.14787900000000001</v>
       </c>
-    </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N363" t="str">
+        <f t="shared" si="5"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>373</v>
       </c>
@@ -17777,8 +19244,12 @@
       <c r="M364">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N364" t="str">
+        <f t="shared" si="5"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>374</v>
       </c>
@@ -17818,8 +19289,12 @@
       <c r="M365">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N365" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>376</v>
       </c>
@@ -17859,8 +19334,12 @@
       <c r="M366">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N366" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>377</v>
       </c>
@@ -17900,8 +19379,12 @@
       <c r="M367">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N367" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>378</v>
       </c>
@@ -17941,8 +19424,12 @@
       <c r="M368">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N368" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>379</v>
       </c>
@@ -17982,8 +19469,12 @@
       <c r="M369">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N369" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>380</v>
       </c>
@@ -18023,8 +19514,12 @@
       <c r="M370">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N370" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>381</v>
       </c>
@@ -18064,8 +19559,12 @@
       <c r="M371">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N371" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>382</v>
       </c>
@@ -18105,8 +19604,12 @@
       <c r="M372">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N372" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>383</v>
       </c>
@@ -18146,8 +19649,12 @@
       <c r="M373">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N373" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>384</v>
       </c>
@@ -18187,8 +19694,12 @@
       <c r="M374">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N374" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>385</v>
       </c>
@@ -18228,8 +19739,12 @@
       <c r="M375">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N375" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>386</v>
       </c>
@@ -18269,8 +19784,12 @@
       <c r="M376">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N376" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>387</v>
       </c>
@@ -18310,8 +19829,12 @@
       <c r="M377">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N377" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>388</v>
       </c>
@@ -18351,8 +19874,12 @@
       <c r="M378">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N378" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>389</v>
       </c>
@@ -18392,8 +19919,12 @@
       <c r="M379">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N379" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>390</v>
       </c>
@@ -18433,8 +19964,12 @@
       <c r="M380">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N380" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>391</v>
       </c>
@@ -18474,8 +20009,12 @@
       <c r="M381">
         <v>4.0334000000000002E-2</v>
       </c>
-    </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N381" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>392</v>
       </c>
@@ -18515,8 +20054,12 @@
       <c r="M382">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N382" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>393</v>
       </c>
@@ -18556,8 +20099,12 @@
       <c r="M383">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N383" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>394</v>
       </c>
@@ -18597,8 +20144,12 @@
       <c r="M384">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N384" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>395</v>
       </c>
@@ -18638,8 +20189,12 @@
       <c r="M385">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N385" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>396</v>
       </c>
@@ -18679,8 +20234,12 @@
       <c r="M386">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N386" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>397</v>
       </c>
@@ -18720,8 +20279,12 @@
       <c r="M387">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N387" t="str">
+        <f t="shared" si="5"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>398</v>
       </c>
@@ -18761,8 +20324,12 @@
       <c r="M388">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N388" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>399</v>
       </c>
@@ -18802,8 +20369,12 @@
       <c r="M389">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N389" t="str">
+        <f t="shared" si="5"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>400</v>
       </c>
@@ -18843,8 +20414,12 @@
       <c r="M390">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N390" t="str">
+        <f t="shared" si="5"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>401</v>
       </c>
@@ -18884,8 +20459,12 @@
       <c r="M391">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N391" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>402</v>
       </c>
@@ -18925,8 +20504,12 @@
       <c r="M392">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N392" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>403</v>
       </c>
@@ -18966,8 +20549,12 @@
       <c r="M393">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N393" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>404</v>
       </c>
@@ -19007,8 +20594,12 @@
       <c r="M394">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N394" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>405</v>
       </c>
@@ -19048,8 +20639,12 @@
       <c r="M395">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N395" t="str">
+        <f t="shared" si="5"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>406</v>
       </c>
@@ -19089,8 +20684,12 @@
       <c r="M396">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N396" t="str">
+        <f t="shared" si="5"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>407</v>
       </c>
@@ -19130,8 +20729,12 @@
       <c r="M397">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N397" t="str">
+        <f t="shared" si="5"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>408</v>
       </c>
@@ -19171,8 +20774,12 @@
       <c r="M398">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N398" t="str">
+        <f t="shared" si="5"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>409</v>
       </c>
@@ -19212,8 +20819,12 @@
       <c r="M399">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N399" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>410</v>
       </c>
@@ -19253,8 +20864,12 @@
       <c r="M400">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N400" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>411</v>
       </c>
@@ -19294,8 +20909,12 @@
       <c r="M401">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N401" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>412</v>
       </c>
@@ -19335,8 +20954,12 @@
       <c r="M402">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N402" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>413</v>
       </c>
@@ -19376,8 +20999,12 @@
       <c r="M403">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N403" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>414</v>
       </c>
@@ -19417,8 +21044,12 @@
       <c r="M404">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N404" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>415</v>
       </c>
@@ -19458,8 +21089,12 @@
       <c r="M405">
         <v>2.0999999999999999E-5</v>
       </c>
-    </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N405" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>416</v>
       </c>
@@ -19499,8 +21134,12 @@
       <c r="M406">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N406" t="str">
+        <f t="shared" si="5"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>417</v>
       </c>
@@ -19540,8 +21179,12 @@
       <c r="M407">
         <v>0.50028099999999998</v>
       </c>
-    </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N407" t="str">
+        <f t="shared" ref="N407:N470" si="6">INDEX($C$1:$M$1, MATCH(MAX(C407:M407), C407:M407, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>418</v>
       </c>
@@ -19581,8 +21224,12 @@
       <c r="M408">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N408" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>419</v>
       </c>
@@ -19622,8 +21269,12 @@
       <c r="M409">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N409" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>420</v>
       </c>
@@ -19663,8 +21314,12 @@
       <c r="M410">
         <v>0.72277599999999997</v>
       </c>
-    </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N410" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>421</v>
       </c>
@@ -19704,8 +21359,12 @@
       <c r="M411">
         <v>0.99984300000000004</v>
       </c>
-    </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N411" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>422</v>
       </c>
@@ -19745,8 +21404,12 @@
       <c r="M412">
         <v>0.440938</v>
       </c>
-    </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N412" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>423</v>
       </c>
@@ -19786,8 +21449,12 @@
       <c r="M413">
         <v>0.99983900000000003</v>
       </c>
-    </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N413" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>424</v>
       </c>
@@ -19827,8 +21494,12 @@
       <c r="M414">
         <v>0.99982899999999997</v>
       </c>
-    </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N414" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>425</v>
       </c>
@@ -19868,8 +21539,12 @@
       <c r="M415">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N415" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>426</v>
       </c>
@@ -19909,8 +21584,12 @@
       <c r="M416">
         <v>0.86531599999999997</v>
       </c>
-    </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N416" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>427</v>
       </c>
@@ -19950,8 +21629,12 @@
       <c r="M417">
         <v>0.77954400000000001</v>
       </c>
-    </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N417" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>428</v>
       </c>
@@ -19991,8 +21674,12 @@
       <c r="M418">
         <v>0.78356999999999999</v>
       </c>
-    </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N418" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>429</v>
       </c>
@@ -20032,8 +21719,12 @@
       <c r="M419">
         <v>0.85633599999999999</v>
       </c>
-    </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N419" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>430</v>
       </c>
@@ -20073,8 +21764,12 @@
       <c r="M420">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N420" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>431</v>
       </c>
@@ -20114,8 +21809,12 @@
       <c r="M421">
         <v>0.11597</v>
       </c>
-    </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N421" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>432</v>
       </c>
@@ -20155,8 +21854,12 @@
       <c r="M422">
         <v>0.56492399999999998</v>
       </c>
-    </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N422" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>433</v>
       </c>
@@ -20196,8 +21899,12 @@
       <c r="M423">
         <v>0.142347</v>
       </c>
-    </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N423" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>434</v>
       </c>
@@ -20237,8 +21944,12 @@
       <c r="M424">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N424" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>435</v>
       </c>
@@ -20278,8 +21989,12 @@
       <c r="M425">
         <v>0.78429400000000005</v>
       </c>
-    </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N425" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>436</v>
       </c>
@@ -20319,8 +22034,12 @@
       <c r="M426">
         <v>0.70584199999999997</v>
       </c>
-    </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N426" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>437</v>
       </c>
@@ -20360,8 +22079,12 @@
       <c r="M427">
         <v>0.422095</v>
       </c>
-    </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N427" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>438</v>
       </c>
@@ -20401,8 +22124,12 @@
       <c r="M428">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N428" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>439</v>
       </c>
@@ -20442,8 +22169,12 @@
       <c r="M429">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N429" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>440</v>
       </c>
@@ -20483,8 +22214,12 @@
       <c r="M430">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N430" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>441</v>
       </c>
@@ -20524,8 +22259,12 @@
       <c r="M431">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N431" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>442</v>
       </c>
@@ -20565,8 +22304,12 @@
       <c r="M432">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N432" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>443</v>
       </c>
@@ -20606,8 +22349,12 @@
       <c r="M433">
         <v>0.78198999999999996</v>
       </c>
-    </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N433" t="str">
+        <f t="shared" si="6"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>444</v>
       </c>
@@ -20647,8 +22394,12 @@
       <c r="M434">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N434" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>445</v>
       </c>
@@ -20688,8 +22439,12 @@
       <c r="M435">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N435" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>446</v>
       </c>
@@ -20729,8 +22484,12 @@
       <c r="M436">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N436" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>447</v>
       </c>
@@ -20770,8 +22529,12 @@
       <c r="M437">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N437" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>448</v>
       </c>
@@ -20811,8 +22574,12 @@
       <c r="M438">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N438" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>449</v>
       </c>
@@ -20852,8 +22619,12 @@
       <c r="M439">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N439" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>450</v>
       </c>
@@ -20893,8 +22664,12 @@
       <c r="M440">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N440" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>451</v>
       </c>
@@ -20934,8 +22709,12 @@
       <c r="M441">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N441" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>452</v>
       </c>
@@ -20975,8 +22754,12 @@
       <c r="M442">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N442" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>453</v>
       </c>
@@ -21016,8 +22799,12 @@
       <c r="M443">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N443" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>454</v>
       </c>
@@ -21057,8 +22844,12 @@
       <c r="M444">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N444" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>455</v>
       </c>
@@ -21098,8 +22889,12 @@
       <c r="M445">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N445" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>456</v>
       </c>
@@ -21139,8 +22934,12 @@
       <c r="M446">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N446" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>457</v>
       </c>
@@ -21180,8 +22979,12 @@
       <c r="M447">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N447" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>458</v>
       </c>
@@ -21221,8 +23024,12 @@
       <c r="M448">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N448" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>459</v>
       </c>
@@ -21262,8 +23069,12 @@
       <c r="M449">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N449" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>460</v>
       </c>
@@ -21303,8 +23114,12 @@
       <c r="M450">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N450" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>461</v>
       </c>
@@ -21344,8 +23159,12 @@
       <c r="M451">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N451" t="str">
+        <f t="shared" si="6"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>462</v>
       </c>
@@ -21385,8 +23204,12 @@
       <c r="M452">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N452" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>463</v>
       </c>
@@ -21426,8 +23249,12 @@
       <c r="M453">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N453" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>464</v>
       </c>
@@ -21467,8 +23294,12 @@
       <c r="M454">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N454" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>465</v>
       </c>
@@ -21508,8 +23339,12 @@
       <c r="M455">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N455" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>466</v>
       </c>
@@ -21549,8 +23384,12 @@
       <c r="M456">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N456" t="str">
+        <f t="shared" si="6"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>467</v>
       </c>
@@ -21590,8 +23429,12 @@
       <c r="M457">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N457" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>468</v>
       </c>
@@ -21631,8 +23474,12 @@
       <c r="M458">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N458" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>469</v>
       </c>
@@ -21672,8 +23519,12 @@
       <c r="M459">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N459" t="str">
+        <f t="shared" si="6"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>470</v>
       </c>
@@ -21713,8 +23564,12 @@
       <c r="M460">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N460" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>471</v>
       </c>
@@ -21754,8 +23609,12 @@
       <c r="M461">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N461" t="str">
+        <f t="shared" si="6"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>472</v>
       </c>
@@ -21795,8 +23654,12 @@
       <c r="M462">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N462" t="str">
+        <f t="shared" si="6"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>473</v>
       </c>
@@ -21836,8 +23699,12 @@
       <c r="M463">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N463" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>474</v>
       </c>
@@ -21877,8 +23744,12 @@
       <c r="M464">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N464" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>475</v>
       </c>
@@ -21918,8 +23789,12 @@
       <c r="M465">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N465" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>476</v>
       </c>
@@ -21959,8 +23834,12 @@
       <c r="M466">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N466" t="str">
+        <f t="shared" si="6"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>477</v>
       </c>
@@ -22000,8 +23879,12 @@
       <c r="M467">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N467" t="str">
+        <f t="shared" si="6"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>478</v>
       </c>
@@ -22041,8 +23924,12 @@
       <c r="M468">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N468" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>479</v>
       </c>
@@ -22082,8 +23969,12 @@
       <c r="M469">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N469" t="str">
+        <f t="shared" si="6"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>480</v>
       </c>
@@ -22123,8 +24014,12 @@
       <c r="M470">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N470" t="str">
+        <f t="shared" si="6"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>481</v>
       </c>
@@ -22164,8 +24059,12 @@
       <c r="M471">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N471" t="str">
+        <f t="shared" ref="N471:N534" si="7">INDEX($C$1:$M$1, MATCH(MAX(C471:M471), C471:M471, 0))</f>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>482</v>
       </c>
@@ -22205,8 +24104,12 @@
       <c r="M472">
         <v>0.11870799999999999</v>
       </c>
-    </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N472" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>483</v>
       </c>
@@ -22246,8 +24149,12 @@
       <c r="M473">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N473" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>484</v>
       </c>
@@ -22287,8 +24194,12 @@
       <c r="M474">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N474" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>485</v>
       </c>
@@ -22328,8 +24239,12 @@
       <c r="M475">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N475" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>486</v>
       </c>
@@ -22369,8 +24284,12 @@
       <c r="M476">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N476" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>487</v>
       </c>
@@ -22410,8 +24329,12 @@
       <c r="M477">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N477" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>488</v>
       </c>
@@ -22451,8 +24374,12 @@
       <c r="M478">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N478" t="str">
+        <f t="shared" si="7"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>489</v>
       </c>
@@ -22492,8 +24419,12 @@
       <c r="M479">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N479" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>490</v>
       </c>
@@ -22533,8 +24464,12 @@
       <c r="M480">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N480" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>491</v>
       </c>
@@ -22574,8 +24509,12 @@
       <c r="M481">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N481" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>492</v>
       </c>
@@ -22615,8 +24554,12 @@
       <c r="M482">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N482" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>493</v>
       </c>
@@ -22656,8 +24599,12 @@
       <c r="M483">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N483" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>494</v>
       </c>
@@ -22697,8 +24644,12 @@
       <c r="M484">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N484" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>495</v>
       </c>
@@ -22738,8 +24689,12 @@
       <c r="M485">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N485" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>496</v>
       </c>
@@ -22779,8 +24734,12 @@
       <c r="M486">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N486" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>497</v>
       </c>
@@ -22820,8 +24779,12 @@
       <c r="M487">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N487" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>498</v>
       </c>
@@ -22861,8 +24824,12 @@
       <c r="M488">
         <v>2.1999999999999999E-5</v>
       </c>
-    </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N488" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>499</v>
       </c>
@@ -22902,8 +24869,12 @@
       <c r="M489">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N489" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>500</v>
       </c>
@@ -22943,8 +24914,12 @@
       <c r="M490">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N490" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>501</v>
       </c>
@@ -22984,8 +24959,12 @@
       <c r="M491">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N491" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>502</v>
       </c>
@@ -23025,8 +25004,12 @@
       <c r="M492">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N492" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>503</v>
       </c>
@@ -23066,8 +25049,12 @@
       <c r="M493">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N493" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>504</v>
       </c>
@@ -23107,8 +25094,12 @@
       <c r="M494">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N494" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>505</v>
       </c>
@@ -23148,8 +25139,12 @@
       <c r="M495">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N495" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>506</v>
       </c>
@@ -23189,8 +25184,12 @@
       <c r="M496">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N496" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>507</v>
       </c>
@@ -23230,8 +25229,12 @@
       <c r="M497">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N497" t="str">
+        <f t="shared" si="7"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>508</v>
       </c>
@@ -23271,8 +25274,12 @@
       <c r="M498">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N498" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>509</v>
       </c>
@@ -23312,8 +25319,12 @@
       <c r="M499">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N499" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>510</v>
       </c>
@@ -23353,8 +25364,12 @@
       <c r="M500">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N500" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>511</v>
       </c>
@@ -23394,8 +25409,12 @@
       <c r="M501">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N501" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>512</v>
       </c>
@@ -23435,8 +25454,12 @@
       <c r="M502">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N502" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>513</v>
       </c>
@@ -23476,8 +25499,12 @@
       <c r="M503">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N503" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>514</v>
       </c>
@@ -23517,8 +25544,12 @@
       <c r="M504">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N504" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>515</v>
       </c>
@@ -23558,8 +25589,12 @@
       <c r="M505">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N505" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>516</v>
       </c>
@@ -23599,8 +25634,12 @@
       <c r="M506">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N506" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>517</v>
       </c>
@@ -23640,8 +25679,12 @@
       <c r="M507">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N507" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>518</v>
       </c>
@@ -23681,8 +25724,12 @@
       <c r="M508">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N508" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>519</v>
       </c>
@@ -23722,8 +25769,12 @@
       <c r="M509">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N509" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>520</v>
       </c>
@@ -23763,8 +25814,12 @@
       <c r="M510">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N510" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>521</v>
       </c>
@@ -23804,8 +25859,12 @@
       <c r="M511">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N511" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>522</v>
       </c>
@@ -23845,8 +25904,12 @@
       <c r="M512">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N512" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>523</v>
       </c>
@@ -23886,8 +25949,12 @@
       <c r="M513">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N513" t="str">
+        <f t="shared" si="7"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="514" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>525</v>
       </c>
@@ -23927,8 +25994,12 @@
       <c r="M514">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N514" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="515" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>526</v>
       </c>
@@ -23968,8 +26039,12 @@
       <c r="M515">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N515" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>527</v>
       </c>
@@ -24009,8 +26084,12 @@
       <c r="M516">
         <v>0.60774899999999998</v>
       </c>
-    </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N516" t="str">
+        <f t="shared" si="7"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>528</v>
       </c>
@@ -24050,8 +26129,12 @@
       <c r="M517">
         <v>0.89269799999999999</v>
       </c>
-    </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N517" t="str">
+        <f t="shared" si="7"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="518" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>529</v>
       </c>
@@ -24091,8 +26174,12 @@
       <c r="M518">
         <v>0.14044300000000001</v>
       </c>
-    </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N518" t="str">
+        <f t="shared" si="7"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>530</v>
       </c>
@@ -24132,8 +26219,12 @@
       <c r="M519">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N519" t="str">
+        <f t="shared" si="7"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="520" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>531</v>
       </c>
@@ -24173,8 +26264,12 @@
       <c r="M520">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N520" t="str">
+        <f t="shared" si="7"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="521" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>532</v>
       </c>
@@ -24214,8 +26309,12 @@
       <c r="M521">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N521" t="str">
+        <f t="shared" si="7"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="522" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>533</v>
       </c>
@@ -24255,8 +26354,12 @@
       <c r="M522">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N522" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="523" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>534</v>
       </c>
@@ -24296,8 +26399,12 @@
       <c r="M523">
         <v>1.9000000000000001E-5</v>
       </c>
-    </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N523" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="524" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>535</v>
       </c>
@@ -24337,8 +26444,12 @@
       <c r="M524">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N524" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="525" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>536</v>
       </c>
@@ -24378,8 +26489,12 @@
       <c r="M525">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N525" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="526" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>537</v>
       </c>
@@ -24419,8 +26534,12 @@
       <c r="M526">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N526" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="527" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>538</v>
       </c>
@@ -24460,8 +26579,12 @@
       <c r="M527">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N527" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="528" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>539</v>
       </c>
@@ -24501,8 +26624,12 @@
       <c r="M528">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N528" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="529" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>540</v>
       </c>
@@ -24542,8 +26669,12 @@
       <c r="M529">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N529" t="str">
+        <f t="shared" si="7"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="530" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>541</v>
       </c>
@@ -24583,8 +26714,12 @@
       <c r="M530">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N530" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="531" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>542</v>
       </c>
@@ -24624,8 +26759,12 @@
       <c r="M531">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N531" t="str">
+        <f t="shared" si="7"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="532" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>543</v>
       </c>
@@ -24665,8 +26804,12 @@
       <c r="M532">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N532" t="str">
+        <f t="shared" si="7"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="533" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>544</v>
       </c>
@@ -24706,8 +26849,12 @@
       <c r="M533">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N533" t="str">
+        <f t="shared" si="7"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="534" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>545</v>
       </c>
@@ -24747,8 +26894,12 @@
       <c r="M534">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N534" t="str">
+        <f t="shared" si="7"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="535" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>546</v>
       </c>
@@ -24788,8 +26939,12 @@
       <c r="M535">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N535" t="str">
+        <f t="shared" ref="N535:N598" si="8">INDEX($C$1:$M$1, MATCH(MAX(C535:M535), C535:M535, 0))</f>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>547</v>
       </c>
@@ -24829,8 +26984,12 @@
       <c r="M536">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N536" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_brown</v>
+      </c>
+    </row>
+    <row r="537" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>548</v>
       </c>
@@ -24870,8 +27029,12 @@
       <c r="M537">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N537" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="538" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>549</v>
       </c>
@@ -24911,8 +27074,12 @@
       <c r="M538">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N538" t="str">
+        <f t="shared" si="8"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>550</v>
       </c>
@@ -24952,8 +27119,12 @@
       <c r="M539">
         <v>5.5939000000000003E-2</v>
       </c>
-    </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N539" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="540" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>551</v>
       </c>
@@ -24993,8 +27164,12 @@
       <c r="M540">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N540" t="str">
+        <f t="shared" si="8"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="541" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>552</v>
       </c>
@@ -25034,8 +27209,12 @@
       <c r="M541">
         <v>0.741124</v>
       </c>
-    </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N541" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="542" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>553</v>
       </c>
@@ -25075,8 +27254,12 @@
       <c r="M542">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N542" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="543" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>554</v>
       </c>
@@ -25116,8 +27299,12 @@
       <c r="M543">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N543" t="str">
+        <f t="shared" si="8"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="544" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>555</v>
       </c>
@@ -25157,8 +27344,12 @@
       <c r="M544">
         <v>2.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N544" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_blue</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>556</v>
       </c>
@@ -25198,8 +27389,12 @@
       <c r="M545">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N545" t="str">
+        <f t="shared" si="8"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="546" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>557</v>
       </c>
@@ -25239,8 +27434,12 @@
       <c r="M546">
         <v>0.69509299999999996</v>
       </c>
-    </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N546" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>558</v>
       </c>
@@ -25280,8 +27479,12 @@
       <c r="M547">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N547" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="548" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>559</v>
       </c>
@@ -25321,8 +27524,12 @@
       <c r="M548">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N548" t="str">
+        <f t="shared" si="8"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="549" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>560</v>
       </c>
@@ -25362,8 +27569,12 @@
       <c r="M549">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N549" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="550" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>561</v>
       </c>
@@ -25403,8 +27614,12 @@
       <c r="M550">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N550" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="551" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>562</v>
       </c>
@@ -25444,8 +27659,12 @@
       <c r="M551">
         <v>1.7E-5</v>
       </c>
-    </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N551" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="552" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>563</v>
       </c>
@@ -25485,8 +27704,12 @@
       <c r="M552">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N552" t="str">
+        <f t="shared" si="8"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="553" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>564</v>
       </c>
@@ -25526,8 +27749,12 @@
       <c r="M553">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N553" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="554" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>566</v>
       </c>
@@ -25567,8 +27794,12 @@
       <c r="M554">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N554" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="555" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>567</v>
       </c>
@@ -25608,8 +27839,12 @@
       <c r="M555">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N555" t="str">
+        <f t="shared" si="8"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="556" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>568</v>
       </c>
@@ -25649,8 +27884,12 @@
       <c r="M556">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N556" t="str">
+        <f t="shared" si="8"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="557" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>569</v>
       </c>
@@ -25690,8 +27929,12 @@
       <c r="M557">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N557" t="str">
+        <f t="shared" si="8"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="558" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>570</v>
       </c>
@@ -25731,8 +27974,12 @@
       <c r="M558">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N558" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="559" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>571</v>
       </c>
@@ -25772,8 +28019,12 @@
       <c r="M559">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N559" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="560" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>572</v>
       </c>
@@ -25813,8 +28064,12 @@
       <c r="M560">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N560" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="561" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>573</v>
       </c>
@@ -25854,8 +28109,12 @@
       <c r="M561">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N561" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="562" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>574</v>
       </c>
@@ -25895,8 +28154,12 @@
       <c r="M562">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N562" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="563" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>575</v>
       </c>
@@ -25936,8 +28199,12 @@
       <c r="M563">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N563" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="564" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>576</v>
       </c>
@@ -25977,8 +28244,12 @@
       <c r="M564">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N564" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="565" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>577</v>
       </c>
@@ -26018,8 +28289,12 @@
       <c r="M565">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N565" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="566" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>578</v>
       </c>
@@ -26059,8 +28334,12 @@
       <c r="M566">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N566" t="str">
+        <f t="shared" si="8"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="567" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>579</v>
       </c>
@@ -26100,8 +28379,12 @@
       <c r="M567">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N567" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="568" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>580</v>
       </c>
@@ -26141,8 +28424,12 @@
       <c r="M568">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N568" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="569" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>581</v>
       </c>
@@ -26182,8 +28469,12 @@
       <c r="M569">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N569" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="570" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>582</v>
       </c>
@@ -26223,8 +28514,12 @@
       <c r="M570">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N570" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="571" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>583</v>
       </c>
@@ -26264,8 +28559,12 @@
       <c r="M571">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N571" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="572" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>584</v>
       </c>
@@ -26305,8 +28604,12 @@
       <c r="M572">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N572" t="str">
+        <f t="shared" si="8"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="573" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>585</v>
       </c>
@@ -26346,8 +28649,12 @@
       <c r="M573">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N573" t="str">
+        <f t="shared" si="8"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="574" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>586</v>
       </c>
@@ -26387,8 +28694,12 @@
       <c r="M574">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N574" t="str">
+        <f t="shared" si="8"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="575" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>587</v>
       </c>
@@ -26428,8 +28739,12 @@
       <c r="M575">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N575" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="576" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>588</v>
       </c>
@@ -26469,8 +28784,12 @@
       <c r="M576">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N576" t="str">
+        <f t="shared" si="8"/>
+        <v>calycosa_yellow</v>
+      </c>
+    </row>
+    <row r="577" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>589</v>
       </c>
@@ -26510,8 +28829,12 @@
       <c r="M577">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N577" t="str">
+        <f t="shared" si="8"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="578" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>590</v>
       </c>
@@ -26551,8 +28874,12 @@
       <c r="M578">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N578" t="str">
+        <f t="shared" si="8"/>
+        <v>caroliniana</v>
+      </c>
+    </row>
+    <row r="579" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>591</v>
       </c>
@@ -26592,8 +28919,12 @@
       <c r="M579">
         <v>0.99987400000000004</v>
       </c>
-    </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N579" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="580" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>592</v>
       </c>
@@ -26633,8 +28964,12 @@
       <c r="M580">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N580" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="581" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>593</v>
       </c>
@@ -26674,8 +29009,12 @@
       <c r="M581">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N581" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="582" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>594</v>
       </c>
@@ -26715,8 +29054,12 @@
       <c r="M582">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N582" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="583" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>595</v>
       </c>
@@ -26756,8 +29099,12 @@
       <c r="M583">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N583" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="584" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>596</v>
       </c>
@@ -26797,8 +29144,12 @@
       <c r="M584">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N584" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="585" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>597</v>
       </c>
@@ -26838,8 +29189,12 @@
       <c r="M585">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N585" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="586" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>598</v>
       </c>
@@ -26879,8 +29234,12 @@
       <c r="M586">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N586" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="587" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>599</v>
       </c>
@@ -26920,8 +29279,12 @@
       <c r="M587">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N587" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="588" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>600</v>
       </c>
@@ -26961,8 +29324,12 @@
       <c r="M588">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N588" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="589" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>601</v>
       </c>
@@ -27002,8 +29369,12 @@
       <c r="M589">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N589" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="590" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>602</v>
       </c>
@@ -27043,8 +29414,12 @@
       <c r="M590">
         <v>9.0680999999999998E-2</v>
       </c>
-    </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N590" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="591" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>603</v>
       </c>
@@ -27084,8 +29459,12 @@
       <c r="M591">
         <v>2.9481E-2</v>
       </c>
-    </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N591" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="592" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>604</v>
       </c>
@@ -27125,8 +29504,12 @@
       <c r="M592">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N592" t="str">
+        <f t="shared" si="8"/>
+        <v>hirsuticaulis_red</v>
+      </c>
+    </row>
+    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>605</v>
       </c>
@@ -27166,8 +29549,12 @@
       <c r="M593">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N593" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>606</v>
       </c>
@@ -27207,8 +29594,12 @@
       <c r="M594">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N594" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>607</v>
       </c>
@@ -27248,8 +29639,12 @@
       <c r="M595">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N595" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="596" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>608</v>
       </c>
@@ -27289,8 +29684,12 @@
       <c r="M596">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N596" t="str">
+        <f t="shared" si="8"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>609</v>
       </c>
@@ -27330,8 +29729,12 @@
       <c r="M597">
         <v>0.85872000000000004</v>
       </c>
-    </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N597" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>610</v>
       </c>
@@ -27371,8 +29774,12 @@
       <c r="M598">
         <v>0.81148200000000004</v>
       </c>
-    </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N598" t="str">
+        <f t="shared" si="8"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="599" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>611</v>
       </c>
@@ -27412,8 +29819,12 @@
       <c r="M599">
         <v>0.99043700000000001</v>
       </c>
-    </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N599" t="str">
+        <f t="shared" ref="N599:N632" si="9">INDEX($C$1:$M$1, MATCH(MAX(C599:M599), C599:M599, 0))</f>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="600" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>612</v>
       </c>
@@ -27453,8 +29864,12 @@
       <c r="M600">
         <v>0.99987099999999995</v>
       </c>
-    </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N600" t="str">
+        <f t="shared" si="9"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="601" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>613</v>
       </c>
@@ -27494,8 +29909,12 @@
       <c r="M601">
         <v>1.2E-5</v>
       </c>
-    </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N601" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="602" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>614</v>
       </c>
@@ -27535,8 +29954,12 @@
       <c r="M602">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N602" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="603" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>615</v>
       </c>
@@ -27576,8 +29999,12 @@
       <c r="M603">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N603" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>616</v>
       </c>
@@ -27617,8 +30044,12 @@
       <c r="M604">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N604" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="605" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>617</v>
       </c>
@@ -27658,8 +30089,12 @@
       <c r="M605">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N605" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="606" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>618</v>
       </c>
@@ -27699,8 +30134,12 @@
       <c r="M606">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N606" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>619</v>
       </c>
@@ -27740,8 +30179,12 @@
       <c r="M607">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N607" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="608" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>620</v>
       </c>
@@ -27781,8 +30224,12 @@
       <c r="M608">
         <v>1.5E-5</v>
       </c>
-    </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N608" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="609" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>621</v>
       </c>
@@ -27822,8 +30269,12 @@
       <c r="M609">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N609" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="610" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>622</v>
       </c>
@@ -27863,8 +30314,12 @@
       <c r="M610">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N610" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="611" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>623</v>
       </c>
@@ -27904,8 +30359,12 @@
       <c r="M611">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N611" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="612" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>624</v>
       </c>
@@ -27945,8 +30404,12 @@
       <c r="M612">
         <v>1.8E-5</v>
       </c>
-    </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N612" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="613" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>625</v>
       </c>
@@ -27986,8 +30449,12 @@
       <c r="M613">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N613" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="614" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>626</v>
       </c>
@@ -28027,8 +30494,12 @@
       <c r="M614">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N614" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="615" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>627</v>
       </c>
@@ -28068,8 +30539,12 @@
       <c r="M615">
         <v>1.5999999999999999E-5</v>
       </c>
-    </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N615" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="616" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>628</v>
       </c>
@@ -28109,8 +30584,12 @@
       <c r="M616">
         <v>0.96357499999999996</v>
       </c>
-    </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N616" t="str">
+        <f t="shared" si="9"/>
+        <v>brevipetala_pink</v>
+      </c>
+    </row>
+    <row r="617" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>629</v>
       </c>
@@ -28150,8 +30629,12 @@
       <c r="M617">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N617" t="str">
+        <f t="shared" si="9"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="618" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>630</v>
       </c>
@@ -28191,8 +30674,12 @@
       <c r="M618">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N618" t="str">
+        <f t="shared" si="9"/>
+        <v>grayana_orange</v>
+      </c>
+    </row>
+    <row r="619" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>631</v>
       </c>
@@ -28232,8 +30719,12 @@
       <c r="M619">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N619" t="str">
+        <f t="shared" si="9"/>
+        <v>alba_lavender</v>
+      </c>
+    </row>
+    <row r="620" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>632</v>
       </c>
@@ -28273,8 +30764,12 @@
       <c r="M620">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N620" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="621" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>633</v>
       </c>
@@ -28314,8 +30809,12 @@
       <c r="M621">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N621" t="str">
+        <f t="shared" si="9"/>
+        <v>richardsonii</v>
+      </c>
+    </row>
+    <row r="622" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>634</v>
       </c>
@@ -28355,8 +30854,12 @@
       <c r="M622">
         <v>1.4E-5</v>
       </c>
-    </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N622" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="623" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>636</v>
       </c>
@@ -28396,8 +30899,12 @@
       <c r="M623">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N623" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="624" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>637</v>
       </c>
@@ -28437,8 +30944,12 @@
       <c r="M624">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N624" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="625" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>638</v>
       </c>
@@ -28478,8 +30989,12 @@
       <c r="M625">
         <v>0.18321699999999999</v>
       </c>
-    </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N625" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="626" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>639</v>
       </c>
@@ -28519,8 +31034,12 @@
       <c r="M626">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N626" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="627" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>640</v>
       </c>
@@ -28560,8 +31079,12 @@
       <c r="M627">
         <v>0.116983</v>
       </c>
-    </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N627" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="628" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>641</v>
       </c>
@@ -28601,8 +31124,12 @@
       <c r="M628">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N628" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="629" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>642</v>
       </c>
@@ -28642,8 +31169,12 @@
       <c r="M629">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N629" t="str">
+        <f t="shared" si="9"/>
+        <v>americana_green</v>
+      </c>
+    </row>
+    <row r="630" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>643</v>
       </c>
@@ -28683,8 +31214,12 @@
       <c r="M630">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N630" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="631" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>644</v>
       </c>
@@ -28724,8 +31259,12 @@
       <c r="M631">
         <v>1.2999999999999999E-5</v>
       </c>
-    </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N631" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
+    </row>
+    <row r="632" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>645</v>
       </c>
@@ -28765,9 +31304,13 @@
       <c r="M632">
         <v>1.2999999999999999E-5</v>
       </c>
+      <c r="N632" t="str">
+        <f t="shared" si="9"/>
+        <v>fumosimontana</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:M1048576">
+  <conditionalFormatting sqref="C1:M1048576 N1">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -28780,5 +31323,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>